--- a/40_AWS/06_コスト調査/AWSコスト推移表.xlsx
+++ b/40_AWS/06_コスト調査/AWSコスト推移表.xlsx
@@ -21,21 +21,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="104">
   <si>
     <t xml:space="preserve">月</t>
   </si>
   <si>
-    <t xml:space="preserve">合計</t>
+    <t xml:space="preserve">合計（税込）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">サービス小計</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tax</t>
   </si>
   <si>
     <t xml:space="preserve">RDS</t>
   </si>
   <si>
     <t xml:space="preserve">TF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tax</t>
   </si>
   <si>
     <t xml:space="preserve">EC2</t>
@@ -48,6 +51,7 @@
       <rPr>
         <b val="true"/>
         <sz val="8"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="0"/>
         <charset val="1"/>
@@ -58,6 +62,7 @@
       <rPr>
         <b val="true"/>
         <sz val="8"/>
+        <color rgb="FF000000"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
@@ -65,13 +70,136 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">カスミPOS  AWS コスト推移表</t>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="16"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">カスミ</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="16"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">POS  AWS </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="16"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">コスト推移表</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">2025/09</t>
   </si>
   <si>
-    <t xml:space="preserve">単位: USD ($)　　■ 網掛け = 実績　　□ 白地 = 未入力（monthly_cost_check.sh 実行後に貼り付け）</t>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="8"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">単位</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="8"/>
+        <color rgb="FF555555"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: USD ($)</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="8"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">　　■ 網掛け </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="8"/>
+        <color rgb="FF555555"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">= </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="8"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">実績　　□ 黄地 </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="8"/>
+        <color rgb="FF555555"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">= </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="8"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未入力（</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="8"/>
+        <color rgb="FF555555"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">monthly_cost_check.sh </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="8"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">実行後に転記）</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">2025/10</t>
@@ -254,15 +382,16 @@
     <t xml:space="preserve">その他</t>
   </si>
   <si>
-    <t xml:space="preserve">前月比 ($)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">前月比 (%)</t>
-  </si>
-  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="8"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">前月比 </t>
+    </r>
     <r>
       <rPr>
         <b val="true"/>
@@ -272,8 +401,13 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">RDS</t>
-    </r>
+      <t xml:space="preserve">($)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">-</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b val="true"/>
@@ -282,11 +416,65 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">前月比 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="8"/>
+        <color rgb="FF555555"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(%)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="8"/>
+        <color rgb="FF555555"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">RDS</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="8"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">比率</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">閾値チェック ($2,500)</t>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="8"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">閾値チェック </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="8"/>
+        <color rgb="FF555555"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">($2,500)</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">月次コスト入力ガイド  —  CloudShell 実行結果の転記手順</t>
@@ -792,12 +980,14 @@
     <font>
       <b val="true"/>
       <sz val="8"/>
+      <color rgb="FF000000"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="8"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
@@ -808,6 +998,13 @@
       <color rgb="FFFFFFFF"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="16"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
@@ -816,20 +1013,11 @@
       <color rgb="FF555555"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
-      <sz val="9"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Noto Sans CJK SC"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="9"/>
-      <color rgb="FFFFFFFF"/>
+      <i val="true"/>
+      <sz val="8"/>
+      <color rgb="FF555555"/>
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
@@ -842,8 +1030,9 @@
       <family val="2"/>
     </font>
     <font>
+      <b val="true"/>
       <sz val="9"/>
-      <color rgb="FF000000"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
@@ -854,7 +1043,6 @@
       <color rgb="FF1A5276"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -862,7 +1050,6 @@
       <color rgb="FF784212"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -883,15 +1070,15 @@
     <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
-      <name val="Noto Sans CJK SC"/>
-      <family val="2"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -899,7 +1086,6 @@
       <color rgb="FFFFFFFF"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -915,6 +1101,13 @@
       <color rgb="FF555555"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="8"/>
+      <color rgb="FF555555"/>
+      <name val="Calibri"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
@@ -932,21 +1125,6 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
-      <sz val="8"/>
-      <color rgb="FF555555"/>
-      <name val="Calibri"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="8"/>
-      <color rgb="FF555555"/>
-      <name val="Noto Sans CJK SC"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="8"/>
       <color rgb="FF1A5276"/>
       <name val="Calibri"/>
@@ -958,7 +1136,6 @@
       <color rgb="FF000000"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -1019,11 +1196,25 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <b val="true"/>
+      <sz val="9"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <sz val="8"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="0"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
@@ -1033,13 +1224,6 @@
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="8"/>
-      <color rgb="FF000000"/>
-      <name val="Noto Sans CJK SC"/>
-      <family val="2"/>
     </font>
     <font>
       <i val="true"/>
@@ -1093,7 +1277,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD6EAF8"/>
-        <bgColor rgb="FFE8EAED"/>
+        <bgColor rgb="FFEBF5FB"/>
       </patternFill>
     </fill>
     <fill>
@@ -1116,14 +1300,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF4F6F7"/>
-        <bgColor rgb="FFF8F9FA"/>
+        <fgColor rgb="FFFEF9E7"/>
+        <bgColor rgb="FFFFFDE7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFEF9E7"/>
-        <bgColor rgb="FFFFFDE7"/>
+        <fgColor rgb="FFF4F6F7"/>
+        <bgColor rgb="FFF8F9FA"/>
       </patternFill>
     </fill>
     <fill>
@@ -1133,7 +1317,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="2">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -1144,39 +1328,6 @@
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
-      <top style="thin">
-        <color rgb="FFD5D8DC"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFD5D8DC"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FFD5D8DC"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left/>
-      <right style="thin">
-        <color rgb="FFE8EAED"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FFD5D8DC"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left/>
-      <right style="medium">
-        <color rgb="FFAAAAAA"/>
-      </right>
       <top/>
       <bottom style="thin">
         <color rgb="FFD5D8DC"/>
@@ -1209,140 +1360,152 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="54">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="10" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="23" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="23" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="24" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="7" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="8" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="8" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="22" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="22" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="25" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="26" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="32" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="31" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1350,35 +1513,23 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="32" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="33" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="34" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="34" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="26" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="35" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="26" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="35" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1386,6 +1537,22 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="36" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="37" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="39" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1394,19 +1561,19 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="33" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="32" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="34" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1426,7 +1593,7 @@
       <rgbColor rgb="FFFF0000"/>
       <rgbColor rgb="FF00FF00"/>
       <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFEF9E7"/>
+      <rgbColor rgb="FFF8F9FA"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FF00FFFF"/>
       <rgbColor rgb="FF800000"/>
@@ -1437,7 +1604,7 @@
       <rgbColor rgb="FF2980B9"/>
       <rgbColor rgb="FFB3B3B3"/>
       <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FFAAAAAA"/>
+      <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFFFFDE7"/>
       <rgbColor rgb="FFD6EAF8"/>
@@ -1447,7 +1614,7 @@
       <rgbColor rgb="FFD5D8DC"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFF8F9FA"/>
+      <rgbColor rgb="FFFDFEFE"/>
       <rgbColor rgb="FF00FFFF"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF800000"/>
@@ -1455,16 +1622,16 @@
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFEBF5FB"/>
-      <rgbColor rgb="FFE8EAED"/>
+      <rgbColor rgb="FFF4F6F7"/>
       <rgbColor rgb="FFFDEBD0"/>
       <rgbColor rgb="FFAED6F1"/>
-      <rgbColor rgb="FFF4F6F7"/>
+      <rgbColor rgb="FFFEF9E7"/>
       <rgbColor rgb="FFD9D9D9"/>
       <rgbColor rgb="FFF0B27A"/>
       <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF85C1E9"/>
+      <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFDFEFE"/>
+      <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFE67E22"/>
       <rgbColor rgb="FF555555"/>
@@ -1508,7 +1675,7 @@
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:rPr>
-              <a:t>月次合計コスト推移 (USD)</a:t>
+              <a:t>月次コスト推移 (USD)</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -1531,11 +1698,125 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>"月間合計 ($)"</c:f>
+              <c:f>"合計（税込）"</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>月間合計 ($)</c:v>
+                  <c:v>合計（税込）</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="1a3a5c"/>
+            </a:solidFill>
+            <a:ln w="24840">
+              <a:solidFill>
+                <a:srgbClr val="1a3a5c"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="6"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="1a3a5c"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>コスト推移表!$AP$2:$AP$7</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>2025/09</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2025/10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2025/11</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2025/12</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2026/01</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2026/02</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>コスト推移表!$AQ$2:$AQ$7</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0.00</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>3316.36</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3455.32</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3483.88</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3904.08</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3910.71</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3586.79</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"サービス小計"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>サービス小計</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1544,7 +1825,7 @@
             <a:solidFill>
               <a:srgbClr val="2e86ab"/>
             </a:solidFill>
-            <a:ln w="24840">
+            <a:ln w="20160">
               <a:solidFill>
                 <a:srgbClr val="2e86ab"/>
               </a:solidFill>
@@ -1552,8 +1833,8 @@
             </a:ln>
           </c:spPr>
           <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="7"/>
+            <c:symbol val="diamond"/>
+            <c:size val="6"/>
             <c:spPr>
               <a:solidFill>
                 <a:srgbClr val="2e86ab"/>
@@ -1613,27 +1894,141 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>コスト推移表!$AQ$2:$AQ$7</c:f>
+              <c:f>コスト推移表!$AR$2:$AR$7</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>3316.36</c:v>
+                  <c:v>3014.87</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3455.32</c:v>
+                  <c:v>3141.14</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3483.88</c:v>
+                  <c:v>3165.79</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3904.08</c:v>
+                  <c:v>3548.79</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3910.71</c:v>
+                  <c:v>3554.63</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3586.79</c:v>
+                  <c:v>3260.71</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"Tax"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Tax</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="e67e22"/>
+            </a:solidFill>
+            <a:ln w="15120">
+              <a:solidFill>
+                <a:srgbClr val="e67e22"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="square"/>
+            <c:size val="6"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="e67e22"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>コスト推移表!$AP$2:$AP$7</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>2025/09</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2025/10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2025/11</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2025/12</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2026/01</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2026/02</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>コスト推移表!$AS$2:$AS$7</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0.00</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>301.49</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>314.18</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>318.09</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>355.29</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>356.08</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>326.08</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1648,11 +2043,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="29824750"/>
-        <c:axId val="61041418"/>
+        <c:axId val="49523354"/>
+        <c:axId val="19971383"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="29824750"/>
+        <c:axId val="49523354"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1683,7 +2078,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="61041418"/>
+        <c:crossAx val="19971383"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1691,7 +2086,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="61041418"/>
+        <c:axId val="19971383"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1765,7 +2160,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="29824750"/>
+        <c:crossAx val="49523354"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1843,7 +2238,7 @@
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:rPr>
-              <a:t>サービス別コスト内訳（実績）</a:t>
+              <a:t>サービス別コスト内訳（実績・税抜）</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -1938,7 +2333,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>コスト推移表!$AR$2:$AR$7</c:f>
+              <c:f>コスト推移表!$AT$2:$AT$7</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00</c:formatCode>
                 <c:ptCount val="6"/>
@@ -2040,7 +2435,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>コスト推移表!$AS$2:$AS$7</c:f>
+              <c:f>コスト推移表!$AU$2:$AU$7</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00</c:formatCode>
                 <c:ptCount val="6"/>
@@ -2069,108 +2464,6 @@
         <c:ser>
           <c:idx val="2"/>
           <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>"Tax"</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Tax</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="85c1e9"/>
-            </a:solidFill>
-            <a:ln w="0">
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:txPr>
-              <a:bodyPr wrap="none"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-              </a:p>
-            </c:txPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>コスト推移表!$AP$2:$AP$7</c:f>
-              <c:strCache>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>2025/09</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2025/10</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2025/11</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>2025/12</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>2026/01</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>2026/02</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>コスト推移表!$AT$2:$AT$7</c:f>
-              <c:numCache>
-                <c:formatCode>#,##0.00</c:formatCode>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>301.49</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>314.18</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>318.09</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>355.29</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>356.08</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>326.08</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-        </c:ser>
-        <c:ser>
-          <c:idx val="3"/>
-          <c:order val="3"/>
           <c:tx>
             <c:strRef>
               <c:f>"EC2"</c:f>
@@ -2244,7 +2537,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>コスト推移表!$AU$2:$AU$7</c:f>
+              <c:f>コスト推移表!$AV$2:$AV$7</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00</c:formatCode>
                 <c:ptCount val="6"/>
@@ -2271,8 +2564,8 @@
           </c:val>
         </c:ser>
         <c:ser>
-          <c:idx val="4"/>
-          <c:order val="4"/>
+          <c:idx val="3"/>
+          <c:order val="3"/>
           <c:tx>
             <c:strRef>
               <c:f>"VPC"</c:f>
@@ -2346,7 +2639,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>コスト推移表!$AV$2:$AV$7</c:f>
+              <c:f>コスト推移表!$AW$2:$AW$7</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00</c:formatCode>
                 <c:ptCount val="6"/>
@@ -2373,8 +2666,8 @@
           </c:val>
         </c:ser>
         <c:ser>
-          <c:idx val="5"/>
-          <c:order val="5"/>
+          <c:idx val="4"/>
+          <c:order val="4"/>
           <c:tx>
             <c:strRef>
               <c:f>"EC2その他"</c:f>
@@ -2448,7 +2741,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>コスト推移表!$AW$2:$AW$7</c:f>
+              <c:f>コスト推移表!$AX$2:$AX$7</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00</c:formatCode>
                 <c:ptCount val="6"/>
@@ -2476,11 +2769,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="17797402"/>
-        <c:axId val="48580461"/>
+        <c:axId val="58039036"/>
+        <c:axId val="97717929"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="17797402"/>
+        <c:axId val="58039036"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2511,7 +2804,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="48580461"/>
+        <c:crossAx val="97717929"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2519,7 +2812,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="48580461"/>
+        <c:axId val="97717929"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2593,7 +2886,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="17797402"/>
+        <c:crossAx val="58039036"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2651,14 +2944,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>441360</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>128880</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>249480</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>107640</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2666,8 +2959,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="141120" y="6124680"/>
-        <a:ext cx="7919640" cy="4319640"/>
+        <a:off x="141120" y="6191280"/>
+        <a:ext cx="8639640" cy="4679640"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2681,14 +2974,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>51</xdr:row>
+      <xdr:row>54</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>441360</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>86400</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>249480</xdr:colOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>86760</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2696,8 +2989,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="141120" y="10315440"/>
-        <a:ext cx="7919640" cy="5039640"/>
+        <a:off x="141120" y="10763280"/>
+        <a:ext cx="8639640" cy="5039640"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2890,1361 +3183,1252 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B1:AW29"/>
+  <dimension ref="B1:AX29"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="8.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="4" style="1" width="10.51"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="49" min="42" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="4" style="0" width="10.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="50" min="42" style="0" width="11"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="AP1" s="2" t="s">
+      <c r="AP1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="AQ1" s="2" t="s">
+      <c r="AQ1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="AR1" s="3" t="s">
+      <c r="AR1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AS1" s="3" t="s">
+      <c r="AS1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="AT1" s="3" t="s">
+      <c r="AT1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="AU1" s="3" t="s">
+      <c r="AU1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="AV1" s="3" t="s">
+      <c r="AV1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="AW1" s="3" t="s">
+      <c r="AW1" s="2" t="s">
         <v>7</v>
       </c>
+      <c r="AX1" s="2" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4"/>
-      <c r="AP2" s="1" t="s">
+      <c r="B2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="AQ2" s="5" t="n">
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="AP2" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="AQ2" s="4" t="n">
         <v>3316.36</v>
       </c>
-      <c r="AR2" s="5" t="n">
+      <c r="AR2" s="4" t="n">
+        <v>3014.87</v>
+      </c>
+      <c r="AS2" s="4" t="n">
+        <v>301.49</v>
+      </c>
+      <c r="AT2" s="4" t="n">
         <v>2204.35</v>
       </c>
-      <c r="AS2" s="5" t="n">
+      <c r="AU2" s="4" t="n">
         <v>432.08</v>
       </c>
-      <c r="AT2" s="5" t="n">
-        <v>301.49</v>
-      </c>
-      <c r="AU2" s="5" t="n">
+      <c r="AV2" s="4" t="n">
         <v>133.31</v>
       </c>
-      <c r="AV2" s="5" t="n">
+      <c r="AW2" s="4" t="n">
         <v>128.02</v>
       </c>
-      <c r="AW2" s="5" t="n">
+      <c r="AX2" s="4" t="n">
         <v>46.32</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="6" t="s">
+    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="5"/>
+      <c r="AP3" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="AQ3" s="4" t="n">
+        <v>3455.32</v>
+      </c>
+      <c r="AR3" s="4" t="n">
+        <v>3141.14</v>
+      </c>
+      <c r="AS3" s="4" t="n">
+        <v>314.18</v>
+      </c>
+      <c r="AT3" s="4" t="n">
+        <v>2277.51</v>
+      </c>
+      <c r="AU3" s="4" t="n">
+        <v>446.48</v>
+      </c>
+      <c r="AV3" s="4" t="n">
+        <v>161.89</v>
+      </c>
+      <c r="AW3" s="4" t="n">
+        <v>132.41</v>
+      </c>
+      <c r="AX3" s="4" t="n">
+        <v>47.8</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
-      <c r="O3" s="6"/>
-      <c r="P3" s="6"/>
-      <c r="AP3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="AQ3" s="5" t="n">
-        <v>3455.32</v>
-      </c>
-      <c r="AR3" s="5" t="n">
-        <v>2277.51</v>
-      </c>
-      <c r="AS3" s="5" t="n">
-        <v>446.48</v>
-      </c>
-      <c r="AT3" s="5" t="n">
-        <v>314.18</v>
-      </c>
-      <c r="AU3" s="5" t="n">
-        <v>161.89</v>
-      </c>
-      <c r="AV3" s="5" t="n">
+      <c r="E4" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="M4" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="N4" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="O4" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="AP4" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="AQ4" s="4" t="n">
+        <v>3483.88</v>
+      </c>
+      <c r="AR4" s="4" t="n">
+        <v>3165.79</v>
+      </c>
+      <c r="AS4" s="4" t="n">
+        <v>318.09</v>
+      </c>
+      <c r="AT4" s="4" t="n">
+        <v>2204.53</v>
+      </c>
+      <c r="AU4" s="4" t="n">
+        <v>501.42</v>
+      </c>
+      <c r="AV4" s="4" t="n">
+        <v>173.09</v>
+      </c>
+      <c r="AW4" s="4" t="n">
+        <v>128.02</v>
+      </c>
+      <c r="AX4" s="4" t="n">
+        <v>48.21</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="K5" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="L5" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="M5" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="N5" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="O5" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="P5" s="9"/>
+      <c r="AP5" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="AQ5" s="4" t="n">
+        <v>3904.08</v>
+      </c>
+      <c r="AR5" s="4" t="n">
+        <v>3548.79</v>
+      </c>
+      <c r="AS5" s="4" t="n">
+        <v>355.29</v>
+      </c>
+      <c r="AT5" s="4" t="n">
+        <v>2277.99</v>
+      </c>
+      <c r="AU5" s="4" t="n">
+        <v>669.67</v>
+      </c>
+      <c r="AV5" s="4" t="n">
+        <v>273.17</v>
+      </c>
+      <c r="AW5" s="4" t="n">
         <v>132.41</v>
       </c>
-      <c r="AW3" s="5" t="n">
-        <v>47.8</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="J4" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="K4" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="L4" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="M4" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="N4" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="O4" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="AP4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="AQ4" s="5" t="n">
-        <v>3483.88</v>
-      </c>
-      <c r="AR4" s="5" t="n">
-        <v>2204.53</v>
-      </c>
-      <c r="AS4" s="5" t="n">
-        <v>501.42</v>
-      </c>
-      <c r="AT4" s="5" t="n">
-        <v>318.09</v>
-      </c>
-      <c r="AU4" s="5" t="n">
-        <v>173.09</v>
-      </c>
-      <c r="AV4" s="5" t="n">
-        <v>128.02</v>
-      </c>
-      <c r="AW4" s="5" t="n">
-        <v>48.21</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="G5" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="H5" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="I5" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="J5" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="K5" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="L5" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="M5" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="N5" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="O5" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="AP5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="AQ5" s="5" t="n">
-        <v>3904.08</v>
-      </c>
-      <c r="AR5" s="5" t="n">
-        <v>2277.99</v>
-      </c>
-      <c r="AS5" s="5" t="n">
-        <v>669.67</v>
-      </c>
-      <c r="AT5" s="5" t="n">
-        <v>355.29</v>
-      </c>
-      <c r="AU5" s="5" t="n">
-        <v>273.17</v>
-      </c>
-      <c r="AV5" s="5" t="n">
-        <v>132.41</v>
-      </c>
-      <c r="AW5" s="5" t="n">
+      <c r="AX5" s="4" t="n">
         <v>59.88</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" s="14" t="n">
+      <c r="B6" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="13" t="n">
         <f aca="false">IFERROR(AVERAGE(D6,E6,F6,G6,H6,I6),"")</f>
         <v>2217.625</v>
       </c>
-      <c r="D6" s="15" t="n">
+      <c r="D6" s="14" t="n">
         <v>2204.35</v>
       </c>
-      <c r="E6" s="15" t="n">
+      <c r="E6" s="14" t="n">
         <v>2277.51</v>
       </c>
-      <c r="F6" s="15" t="n">
+      <c r="F6" s="14" t="n">
         <v>2204.53</v>
       </c>
-      <c r="G6" s="15" t="n">
+      <c r="G6" s="14" t="n">
         <v>2277.99</v>
       </c>
-      <c r="H6" s="15" t="n">
+      <c r="H6" s="14" t="n">
         <v>2280.3</v>
       </c>
-      <c r="I6" s="15" t="n">
+      <c r="I6" s="14" t="n">
         <v>2061.07</v>
       </c>
-      <c r="J6" s="16"/>
-      <c r="K6" s="16"/>
-      <c r="L6" s="16"/>
-      <c r="M6" s="16"/>
-      <c r="N6" s="16"/>
-      <c r="O6" s="17"/>
-      <c r="AP6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="AQ6" s="5" t="n">
+      <c r="J6" s="15"/>
+      <c r="K6" s="15"/>
+      <c r="L6" s="15"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="15"/>
+      <c r="O6" s="15"/>
+      <c r="AP6" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="AQ6" s="4" t="n">
         <v>3910.71</v>
       </c>
-      <c r="AR6" s="5" t="n">
+      <c r="AR6" s="4" t="n">
+        <v>3554.63</v>
+      </c>
+      <c r="AS6" s="4" t="n">
+        <v>356.08</v>
+      </c>
+      <c r="AT6" s="4" t="n">
         <v>2280.3</v>
       </c>
-      <c r="AS6" s="5" t="n">
+      <c r="AU6" s="4" t="n">
         <v>669.71</v>
       </c>
-      <c r="AT6" s="5" t="n">
-        <v>356.08</v>
-      </c>
-      <c r="AU6" s="5" t="n">
+      <c r="AV6" s="4" t="n">
         <v>272.97</v>
       </c>
-      <c r="AV6" s="5" t="n">
+      <c r="AW6" s="4" t="n">
         <v>130.21</v>
       </c>
-      <c r="AW6" s="5" t="n">
+      <c r="AX6" s="4" t="n">
         <v>60.79</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" s="14" t="n">
+      <c r="B7" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="13" t="n">
         <f aca="false">IFERROR(AVERAGE(D7,E7,F7,G7,H7,I7),"")</f>
         <v>554.051666666667</v>
       </c>
-      <c r="D7" s="15" t="n">
+      <c r="D7" s="14" t="n">
         <v>432.08</v>
       </c>
-      <c r="E7" s="15" t="n">
+      <c r="E7" s="14" t="n">
         <v>446.48</v>
       </c>
-      <c r="F7" s="15" t="n">
+      <c r="F7" s="14" t="n">
         <v>501.42</v>
       </c>
-      <c r="G7" s="15" t="n">
+      <c r="G7" s="14" t="n">
         <v>669.67</v>
       </c>
-      <c r="H7" s="15" t="n">
+      <c r="H7" s="14" t="n">
         <v>669.71</v>
       </c>
-      <c r="I7" s="15" t="n">
+      <c r="I7" s="14" t="n">
         <v>604.95</v>
       </c>
-      <c r="J7" s="16"/>
-      <c r="K7" s="16"/>
-      <c r="L7" s="16"/>
-      <c r="M7" s="16"/>
-      <c r="N7" s="16"/>
-      <c r="O7" s="17"/>
-      <c r="AP7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="AQ7" s="5" t="n">
+      <c r="J7" s="15"/>
+      <c r="K7" s="15"/>
+      <c r="L7" s="15"/>
+      <c r="M7" s="15"/>
+      <c r="N7" s="15"/>
+      <c r="O7" s="15"/>
+      <c r="AP7" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="AQ7" s="4" t="n">
         <v>3586.79</v>
       </c>
-      <c r="AR7" s="5" t="n">
+      <c r="AR7" s="4" t="n">
+        <v>3260.71</v>
+      </c>
+      <c r="AS7" s="4" t="n">
+        <v>326.08</v>
+      </c>
+      <c r="AT7" s="4" t="n">
         <v>2061.07</v>
       </c>
-      <c r="AS7" s="5" t="n">
+      <c r="AU7" s="4" t="n">
         <v>604.95</v>
       </c>
-      <c r="AT7" s="5" t="n">
+      <c r="AV7" s="4" t="n">
+        <v>246.69</v>
+      </c>
+      <c r="AW7" s="4" t="n">
+        <v>151.66</v>
+      </c>
+      <c r="AX7" s="4" t="n">
+        <v>56.16</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="13" t="n">
+        <f aca="false">IFERROR(AVERAGE(D8,E8,F8,G8,H8,I8),"")</f>
+        <v>210.186666666667</v>
+      </c>
+      <c r="D8" s="14" t="n">
+        <v>133.31</v>
+      </c>
+      <c r="E8" s="14" t="n">
+        <v>161.89</v>
+      </c>
+      <c r="F8" s="14" t="n">
+        <v>173.09</v>
+      </c>
+      <c r="G8" s="14" t="n">
+        <v>273.17</v>
+      </c>
+      <c r="H8" s="14" t="n">
+        <v>272.97</v>
+      </c>
+      <c r="I8" s="14" t="n">
+        <v>246.69</v>
+      </c>
+      <c r="J8" s="15"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="15"/>
+      <c r="M8" s="15"/>
+      <c r="N8" s="15"/>
+      <c r="O8" s="15"/>
+    </row>
+    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="13" t="n">
+        <f aca="false">IFERROR(AVERAGE(D9,E9,F9,G9,H9,I9),"")</f>
+        <v>133.788333333333</v>
+      </c>
+      <c r="D9" s="14" t="n">
+        <v>128.02</v>
+      </c>
+      <c r="E9" s="14" t="n">
+        <v>132.41</v>
+      </c>
+      <c r="F9" s="14" t="n">
+        <v>128.02</v>
+      </c>
+      <c r="G9" s="14" t="n">
+        <v>132.41</v>
+      </c>
+      <c r="H9" s="14" t="n">
+        <v>130.21</v>
+      </c>
+      <c r="I9" s="14" t="n">
+        <v>151.66</v>
+      </c>
+      <c r="J9" s="15"/>
+      <c r="K9" s="15"/>
+      <c r="L9" s="15"/>
+      <c r="M9" s="15"/>
+      <c r="N9" s="15"/>
+      <c r="O9" s="15"/>
+    </row>
+    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="13" t="n">
+        <f aca="false">IFERROR(AVERAGE(D10,E10,F10,G10,H10,I10),"")</f>
+        <v>53.1933333333333</v>
+      </c>
+      <c r="D10" s="14" t="n">
+        <v>46.32</v>
+      </c>
+      <c r="E10" s="14" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="F10" s="14" t="n">
+        <v>48.21</v>
+      </c>
+      <c r="G10" s="14" t="n">
+        <v>59.88</v>
+      </c>
+      <c r="H10" s="14" t="n">
+        <v>60.79</v>
+      </c>
+      <c r="I10" s="14" t="n">
+        <v>56.16</v>
+      </c>
+      <c r="J10" s="15"/>
+      <c r="K10" s="15"/>
+      <c r="L10" s="15"/>
+      <c r="M10" s="15"/>
+      <c r="N10" s="15"/>
+      <c r="O10" s="15"/>
+    </row>
+    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="13" t="n">
+        <f aca="false">IFERROR(AVERAGE(D11,E11,F11,G11,H11,I11),"")</f>
+        <v>24.385</v>
+      </c>
+      <c r="D11" s="14" t="n">
+        <v>23.58</v>
+      </c>
+      <c r="E11" s="14" t="n">
+        <v>12.31</v>
+      </c>
+      <c r="F11" s="14" t="n">
+        <v>20.84</v>
+      </c>
+      <c r="G11" s="14" t="n">
+        <v>27.49</v>
+      </c>
+      <c r="H11" s="14" t="n">
+        <v>31.87</v>
+      </c>
+      <c r="I11" s="14" t="n">
+        <v>30.22</v>
+      </c>
+      <c r="J11" s="15"/>
+      <c r="K11" s="15"/>
+      <c r="L11" s="15"/>
+      <c r="M11" s="15"/>
+      <c r="N11" s="15"/>
+      <c r="O11" s="15"/>
+    </row>
+    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="13" t="n">
+        <f aca="false">IFERROR(AVERAGE(D12,E12,F12,G12,H12,I12),"")</f>
+        <v>21.0866666666667</v>
+      </c>
+      <c r="D12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="14" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="F12" s="14" t="n">
+        <v>29.87</v>
+      </c>
+      <c r="G12" s="14" t="n">
+        <v>30.86</v>
+      </c>
+      <c r="H12" s="14" t="n">
+        <v>30.66</v>
+      </c>
+      <c r="I12" s="14" t="n">
+        <v>30.58</v>
+      </c>
+      <c r="J12" s="15"/>
+      <c r="K12" s="15"/>
+      <c r="L12" s="15"/>
+      <c r="M12" s="15"/>
+      <c r="N12" s="15"/>
+      <c r="O12" s="15"/>
+    </row>
+    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="13" t="n">
+        <f aca="false">IFERROR(AVERAGE(D13,E13,F13,G13,H13,I13),"")</f>
+        <v>17.795</v>
+      </c>
+      <c r="D13" s="14" t="n">
+        <v>15.36</v>
+      </c>
+      <c r="E13" s="14" t="n">
+        <v>14.68</v>
+      </c>
+      <c r="F13" s="14" t="n">
+        <v>17.01</v>
+      </c>
+      <c r="G13" s="14" t="n">
+        <v>19.84</v>
+      </c>
+      <c r="H13" s="14" t="n">
+        <v>20.64</v>
+      </c>
+      <c r="I13" s="14" t="n">
+        <v>19.24</v>
+      </c>
+      <c r="J13" s="15"/>
+      <c r="K13" s="15"/>
+      <c r="L13" s="15"/>
+      <c r="M13" s="15"/>
+      <c r="N13" s="15"/>
+      <c r="O13" s="15"/>
+    </row>
+    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B14" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="13" t="n">
+        <f aca="false">IFERROR(AVERAGE(D14,E14,F14,G14,H14,I14),"")</f>
+        <v>15.66</v>
+      </c>
+      <c r="D14" s="14" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="E14" s="14" t="n">
+        <v>15.16</v>
+      </c>
+      <c r="F14" s="14" t="n">
+        <v>9.91</v>
+      </c>
+      <c r="G14" s="14" t="n">
+        <v>21.15</v>
+      </c>
+      <c r="H14" s="14" t="n">
+        <v>20.56</v>
+      </c>
+      <c r="I14" s="14" t="n">
+        <v>18.28</v>
+      </c>
+      <c r="J14" s="15"/>
+      <c r="K14" s="15"/>
+      <c r="L14" s="15"/>
+      <c r="M14" s="15"/>
+      <c r="N14" s="15"/>
+      <c r="O14" s="15"/>
+    </row>
+    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="13" t="n">
+        <f aca="false">IFERROR(AVERAGE(D15,E15,F15,G15,H15,I15),"")</f>
+        <v>7.6</v>
+      </c>
+      <c r="D15" s="14" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E15" s="14" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="F15" s="14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G15" s="14" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="H15" s="14" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="I15" s="14" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="J15" s="15"/>
+      <c r="K15" s="15"/>
+      <c r="L15" s="15"/>
+      <c r="M15" s="15"/>
+      <c r="N15" s="15"/>
+      <c r="O15" s="15"/>
+    </row>
+    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="13" t="n">
+        <f aca="false">IFERROR(AVERAGE(D16,E16,F16,G16,H16,I16),"")</f>
+        <v>4.62666666666667</v>
+      </c>
+      <c r="D16" s="14" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="E16" s="14" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="F16" s="14" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="G16" s="14" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="H16" s="14" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="I16" s="14" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="J16" s="15"/>
+      <c r="K16" s="15"/>
+      <c r="L16" s="15"/>
+      <c r="M16" s="15"/>
+      <c r="N16" s="15"/>
+      <c r="O16" s="15"/>
+    </row>
+    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" s="13" t="n">
+        <f aca="false">IFERROR(AVERAGE(D17,E17,F17,G17,H17,I17),"")</f>
+        <v>4</v>
+      </c>
+      <c r="D17" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E17" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="F17" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="G17" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="H17" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I17" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="J17" s="15"/>
+      <c r="K17" s="15"/>
+      <c r="L17" s="15"/>
+      <c r="M17" s="15"/>
+      <c r="N17" s="15"/>
+      <c r="O17" s="15"/>
+    </row>
+    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="13" t="n">
+        <f aca="false">IFERROR(AVERAGE(D18,E18,F18,G18,H18,I18),"")</f>
+        <v>2.94</v>
+      </c>
+      <c r="D18" s="14" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="E18" s="14" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="F18" s="14" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="G18" s="14" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="H18" s="14" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="I18" s="14" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="J18" s="15"/>
+      <c r="K18" s="15"/>
+      <c r="L18" s="15"/>
+      <c r="M18" s="15"/>
+      <c r="N18" s="15"/>
+      <c r="O18" s="15"/>
+    </row>
+    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" s="13" t="n">
+        <f aca="false">IFERROR(AVERAGE(D19,E19,F19,G19,H19,I19),"")</f>
+        <v>2.535</v>
+      </c>
+      <c r="D19" s="14" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="E19" s="14" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="F19" s="14" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="G19" s="14" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="H19" s="14" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="I19" s="14" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="J19" s="15"/>
+      <c r="K19" s="15"/>
+      <c r="L19" s="15"/>
+      <c r="M19" s="15"/>
+      <c r="N19" s="15"/>
+      <c r="O19" s="15"/>
+    </row>
+    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" s="13" t="n">
+        <f aca="false">IFERROR(AVERAGE(D20,E20,F20,G20,H20,I20),"")</f>
+        <v>2.10666666666667</v>
+      </c>
+      <c r="D20" s="14" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="E20" s="14" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="F20" s="14" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="G20" s="14" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="H20" s="14" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="I20" s="14" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="J20" s="15"/>
+      <c r="K20" s="15"/>
+      <c r="L20" s="15"/>
+      <c r="M20" s="15"/>
+      <c r="N20" s="15"/>
+      <c r="O20" s="15"/>
+    </row>
+    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" s="13" t="n">
+        <f aca="false">IFERROR(AVERAGE(D21,E21,F21,G21,H21,I21),"")</f>
+        <v>1.49166666666667</v>
+      </c>
+      <c r="D21" s="14" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="E21" s="14" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="F21" s="14" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="G21" s="14" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="H21" s="14" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="I21" s="14" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="J21" s="15"/>
+      <c r="K21" s="15"/>
+      <c r="L21" s="15"/>
+      <c r="M21" s="15"/>
+      <c r="N21" s="15"/>
+      <c r="O21" s="15"/>
+    </row>
+    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22" s="13" t="n">
+        <f aca="false">IFERROR(AVERAGE(D22,E22,F22,G22,H22,I22),"")</f>
+        <v>6.85</v>
+      </c>
+      <c r="D22" s="14" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="E22" s="14" t="n">
+        <v>6.37</v>
+      </c>
+      <c r="F22" s="14" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="G22" s="14" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="H22" s="14" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="I22" s="14" t="n">
+        <v>6.62</v>
+      </c>
+      <c r="J22" s="15"/>
+      <c r="K22" s="15"/>
+      <c r="L22" s="15"/>
+      <c r="M22" s="15"/>
+      <c r="N22" s="15"/>
+      <c r="O22" s="15"/>
+    </row>
+    <row r="23" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B23" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="19" t="n">
+        <f aca="false">IFERROR(SUM(C6,C7,C8,C9,C10,C11,C12,C13,C14,C15,C16,C17,C18,C19,C20,C21,C22),"")</f>
+        <v>3279.92166666667</v>
+      </c>
+      <c r="D23" s="19" t="n">
+        <f aca="false">IFERROR(SUM(D6:D22),"")</f>
+        <v>3014.87</v>
+      </c>
+      <c r="E23" s="19" t="n">
+        <f aca="false">IFERROR(SUM(E6:E22),"")</f>
+        <v>3141.14</v>
+      </c>
+      <c r="F23" s="19" t="n">
+        <f aca="false">IFERROR(SUM(F6:F22),"")</f>
+        <v>3165.79</v>
+      </c>
+      <c r="G23" s="19" t="n">
+        <f aca="false">IFERROR(SUM(G6:G22),"")</f>
+        <v>3548.79</v>
+      </c>
+      <c r="H23" s="19" t="n">
+        <f aca="false">IFERROR(SUM(H6:H22),"")</f>
+        <v>3554.63</v>
+      </c>
+      <c r="I23" s="19" t="n">
+        <f aca="false">IFERROR(SUM(I6:I22),"")</f>
+        <v>3254.31</v>
+      </c>
+      <c r="J23" s="19" t="n">
+        <f aca="false">IFERROR(SUM(J6:J22),"")</f>
+        <v>0</v>
+      </c>
+      <c r="K23" s="19" t="n">
+        <f aca="false">IFERROR(SUM(K6:K22),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L23" s="19" t="n">
+        <f aca="false">IFERROR(SUM(L6:L22),"")</f>
+        <v>0</v>
+      </c>
+      <c r="M23" s="19" t="n">
+        <f aca="false">IFERROR(SUM(M6:M22),"")</f>
+        <v>0</v>
+      </c>
+      <c r="N23" s="19" t="n">
+        <f aca="false">IFERROR(SUM(N6:N22),"")</f>
+        <v>0</v>
+      </c>
+      <c r="O23" s="19" t="n">
+        <f aca="false">IFERROR(SUM(O6:O22),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B24" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="C24" s="13" t="n">
+        <f aca="false">IFERROR(AVERAGE(D24,E24,F24,G24,H24,I24),"")</f>
+        <v>328.535</v>
+      </c>
+      <c r="D24" s="21" t="n">
+        <v>301.49</v>
+      </c>
+      <c r="E24" s="21" t="n">
+        <v>314.18</v>
+      </c>
+      <c r="F24" s="21" t="n">
+        <v>318.09</v>
+      </c>
+      <c r="G24" s="21" t="n">
+        <v>355.29</v>
+      </c>
+      <c r="H24" s="21" t="n">
+        <v>356.08</v>
+      </c>
+      <c r="I24" s="21" t="n">
         <v>326.08</v>
       </c>
-      <c r="AU7" s="5" t="n">
-        <v>246.69</v>
-      </c>
-      <c r="AV7" s="5" t="n">
-        <v>151.66</v>
-      </c>
-      <c r="AW7" s="5" t="n">
-        <v>56.16</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="C8" s="14" t="n">
-        <f aca="false">IFERROR(AVERAGE(D8,E8,F8,G8,H8,I8),"")</f>
-        <v>328.535</v>
-      </c>
-      <c r="D8" s="15" t="n">
-        <v>301.49</v>
-      </c>
-      <c r="E8" s="15" t="n">
-        <v>314.18</v>
-      </c>
-      <c r="F8" s="15" t="n">
-        <v>318.09</v>
-      </c>
-      <c r="G8" s="15" t="n">
-        <v>355.29</v>
-      </c>
-      <c r="H8" s="15" t="n">
-        <v>356.08</v>
-      </c>
-      <c r="I8" s="15" t="n">
-        <v>326.08</v>
-      </c>
-      <c r="J8" s="16"/>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="16"/>
-      <c r="O8" s="17"/>
-      <c r="AP8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="AQ8" s="5" t="n">
-        <f aca="false">J24</f>
+      <c r="J24" s="15"/>
+      <c r="K24" s="15"/>
+      <c r="L24" s="15"/>
+      <c r="M24" s="15"/>
+      <c r="N24" s="15"/>
+      <c r="O24" s="15"/>
+    </row>
+    <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B25" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="C25" s="23" t="n">
+        <f aca="false">IFERROR(C23+C24,"")</f>
+        <v>3608.45666666667</v>
+      </c>
+      <c r="D25" s="23" t="n">
+        <f aca="false">IFERROR(D23+D24,"")</f>
+        <v>3316.36</v>
+      </c>
+      <c r="E25" s="23" t="n">
+        <f aca="false">IFERROR(E23+E24,"")</f>
+        <v>3455.32</v>
+      </c>
+      <c r="F25" s="23" t="n">
+        <f aca="false">IFERROR(F23+F24,"")</f>
+        <v>3483.88</v>
+      </c>
+      <c r="G25" s="23" t="n">
+        <f aca="false">IFERROR(G23+G24,"")</f>
+        <v>3904.08</v>
+      </c>
+      <c r="H25" s="23" t="n">
+        <f aca="false">IFERROR(H23+H24,"")</f>
+        <v>3910.71</v>
+      </c>
+      <c r="I25" s="23" t="n">
+        <f aca="false">IFERROR(I23+I24,"")</f>
+        <v>3580.39</v>
+      </c>
+      <c r="J25" s="23" t="n">
+        <f aca="false">IFERROR(J23+J24,"")</f>
         <v>0</v>
       </c>
-      <c r="AR8" s="5" t="n">
-        <f aca="false">J6</f>
+      <c r="K25" s="23" t="n">
+        <f aca="false">IFERROR(K23+K24,"")</f>
         <v>0</v>
       </c>
-      <c r="AS8" s="5" t="n">
-        <f aca="false">J7</f>
+      <c r="L25" s="23" t="n">
+        <f aca="false">IFERROR(L23+L24,"")</f>
         <v>0</v>
       </c>
-      <c r="AT8" s="5" t="n">
-        <f aca="false">J8</f>
+      <c r="M25" s="23" t="n">
+        <f aca="false">IFERROR(M23+M24,"")</f>
         <v>0</v>
       </c>
-      <c r="AU8" s="5" t="n">
-        <f aca="false">J9</f>
+      <c r="N25" s="23" t="n">
+        <f aca="false">IFERROR(N23+N24,"")</f>
         <v>0</v>
       </c>
-      <c r="AV8" s="5" t="n">
-        <f aca="false">J10</f>
+      <c r="O25" s="23" t="n">
+        <f aca="false">IFERROR(O23+O24,"")</f>
         <v>0</v>
       </c>
-      <c r="AW8" s="5" t="n">
-        <f aca="false">J11</f>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B26" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="C26" s="25"/>
+      <c r="D26" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="E26" s="27" t="n">
+        <f aca="false">IFERROR(E25-D25,"")</f>
+        <v>138.960000000001</v>
+      </c>
+      <c r="F26" s="27" t="n">
+        <f aca="false">IFERROR(F25-E25,"")</f>
+        <v>28.5600000000004</v>
+      </c>
+      <c r="G26" s="27" t="n">
+        <f aca="false">IFERROR(G25-F25,"")</f>
+        <v>420.199999999999</v>
+      </c>
+      <c r="H26" s="27" t="n">
+        <f aca="false">IFERROR(H25-G25,"")</f>
+        <v>6.63000000000011</v>
+      </c>
+      <c r="I26" s="27" t="n">
+        <f aca="false">IFERROR(I25-H25,"")</f>
+        <v>-330.32</v>
+      </c>
+      <c r="J26" s="27" t="n">
+        <f aca="false">IFERROR(J25-I25,"")</f>
+        <v>-3580.39</v>
+      </c>
+      <c r="K26" s="27" t="n">
+        <f aca="false">IFERROR(K25-J25,"")</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" s="14" t="n">
-        <f aca="false">IFERROR(AVERAGE(D9,E9,F9,G9,H9,I9),"")</f>
-        <v>210.186666666667</v>
-      </c>
-      <c r="D9" s="15" t="n">
-        <v>133.31</v>
-      </c>
-      <c r="E9" s="15" t="n">
-        <v>161.89</v>
-      </c>
-      <c r="F9" s="15" t="n">
-        <v>173.09</v>
-      </c>
-      <c r="G9" s="15" t="n">
-        <v>273.17</v>
-      </c>
-      <c r="H9" s="15" t="n">
-        <v>272.97</v>
-      </c>
-      <c r="I9" s="15" t="n">
-        <v>246.69</v>
-      </c>
-      <c r="J9" s="16"/>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="16"/>
-      <c r="O9" s="17"/>
-      <c r="AP9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="AQ9" s="5" t="n">
-        <f aca="false">K24</f>
+      <c r="L26" s="27" t="n">
+        <f aca="false">IFERROR(L25-K25,"")</f>
         <v>0</v>
       </c>
-      <c r="AR9" s="5" t="n">
-        <f aca="false">K6</f>
+      <c r="M26" s="27" t="n">
+        <f aca="false">IFERROR(M25-L25,"")</f>
         <v>0</v>
       </c>
-      <c r="AS9" s="5" t="n">
-        <f aca="false">K7</f>
+      <c r="N26" s="27" t="n">
+        <f aca="false">IFERROR(N25-M25,"")</f>
         <v>0</v>
       </c>
-      <c r="AT9" s="5" t="n">
-        <f aca="false">K8</f>
+      <c r="O26" s="27" t="n">
+        <f aca="false">IFERROR(O25-N25,"")</f>
         <v>0</v>
       </c>
-      <c r="AU9" s="5" t="n">
-        <f aca="false">K9</f>
-        <v>0</v>
-      </c>
-      <c r="AV9" s="5" t="n">
-        <f aca="false">K10</f>
-        <v>0</v>
-      </c>
-      <c r="AW9" s="5" t="n">
-        <f aca="false">K11</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" s="14" t="n">
-        <f aca="false">IFERROR(AVERAGE(D10,E10,F10,G10,H10,I10),"")</f>
-        <v>133.788333333333</v>
-      </c>
-      <c r="D10" s="15" t="n">
-        <v>128.02</v>
-      </c>
-      <c r="E10" s="15" t="n">
-        <v>132.41</v>
-      </c>
-      <c r="F10" s="15" t="n">
-        <v>128.02</v>
-      </c>
-      <c r="G10" s="15" t="n">
-        <v>132.41</v>
-      </c>
-      <c r="H10" s="15" t="n">
-        <v>130.21</v>
-      </c>
-      <c r="I10" s="15" t="n">
-        <v>151.66</v>
-      </c>
-      <c r="J10" s="16"/>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="16"/>
-      <c r="O10" s="17"/>
-      <c r="AP10" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="AQ10" s="5" t="n">
-        <f aca="false">L24</f>
-        <v>0</v>
-      </c>
-      <c r="AR10" s="5" t="n">
-        <f aca="false">L6</f>
-        <v>0</v>
-      </c>
-      <c r="AS10" s="5" t="n">
-        <f aca="false">L7</f>
-        <v>0</v>
-      </c>
-      <c r="AT10" s="5" t="n">
-        <f aca="false">L8</f>
-        <v>0</v>
-      </c>
-      <c r="AU10" s="5" t="n">
-        <f aca="false">L9</f>
-        <v>0</v>
-      </c>
-      <c r="AV10" s="5" t="n">
-        <f aca="false">L10</f>
-        <v>0</v>
-      </c>
-      <c r="AW10" s="5" t="n">
-        <f aca="false">L11</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" s="14" t="n">
-        <f aca="false">IFERROR(AVERAGE(D11,E11,F11,G11,H11,I11),"")</f>
-        <v>53.1933333333333</v>
-      </c>
-      <c r="D11" s="15" t="n">
-        <v>46.32</v>
-      </c>
-      <c r="E11" s="15" t="n">
-        <v>47.8</v>
-      </c>
-      <c r="F11" s="15" t="n">
-        <v>48.21</v>
-      </c>
-      <c r="G11" s="15" t="n">
-        <v>59.88</v>
-      </c>
-      <c r="H11" s="15" t="n">
-        <v>60.79</v>
-      </c>
-      <c r="I11" s="15" t="n">
-        <v>56.16</v>
-      </c>
-      <c r="J11" s="16"/>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="16"/>
-      <c r="O11" s="17"/>
-      <c r="AP11" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="AQ11" s="5" t="n">
-        <f aca="false">M24</f>
-        <v>0</v>
-      </c>
-      <c r="AR11" s="5" t="n">
-        <f aca="false">M6</f>
-        <v>0</v>
-      </c>
-      <c r="AS11" s="5" t="n">
-        <f aca="false">M7</f>
-        <v>0</v>
-      </c>
-      <c r="AT11" s="5" t="n">
-        <f aca="false">M8</f>
-        <v>0</v>
-      </c>
-      <c r="AU11" s="5" t="n">
-        <f aca="false">M9</f>
-        <v>0</v>
-      </c>
-      <c r="AV11" s="5" t="n">
-        <f aca="false">M10</f>
-        <v>0</v>
-      </c>
-      <c r="AW11" s="5" t="n">
-        <f aca="false">M11</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" s="14" t="n">
-        <f aca="false">IFERROR(AVERAGE(D12,E12,F12,G12,H12,I12),"")</f>
-        <v>24.385</v>
-      </c>
-      <c r="D12" s="15" t="n">
-        <v>23.58</v>
-      </c>
-      <c r="E12" s="15" t="n">
-        <v>12.31</v>
-      </c>
-      <c r="F12" s="15" t="n">
-        <v>20.84</v>
-      </c>
-      <c r="G12" s="15" t="n">
-        <v>27.49</v>
-      </c>
-      <c r="H12" s="15" t="n">
-        <v>31.87</v>
-      </c>
-      <c r="I12" s="15" t="n">
-        <v>30.22</v>
-      </c>
-      <c r="J12" s="16"/>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="16"/>
-      <c r="O12" s="17"/>
-      <c r="AP12" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="AQ12" s="5" t="n">
-        <f aca="false">N24</f>
-        <v>0</v>
-      </c>
-      <c r="AR12" s="5" t="n">
-        <f aca="false">N6</f>
-        <v>0</v>
-      </c>
-      <c r="AS12" s="5" t="n">
-        <f aca="false">N7</f>
-        <v>0</v>
-      </c>
-      <c r="AT12" s="5" t="n">
-        <f aca="false">N8</f>
-        <v>0</v>
-      </c>
-      <c r="AU12" s="5" t="n">
-        <f aca="false">N9</f>
-        <v>0</v>
-      </c>
-      <c r="AV12" s="5" t="n">
-        <f aca="false">N10</f>
-        <v>0</v>
-      </c>
-      <c r="AW12" s="5" t="n">
-        <f aca="false">N11</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" s="14" t="n">
-        <f aca="false">IFERROR(AVERAGE(D13,E13,F13,G13,H13,I13),"")</f>
-        <v>21.0866666666667</v>
-      </c>
-      <c r="D13" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="15" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="F13" s="15" t="n">
-        <v>29.87</v>
-      </c>
-      <c r="G13" s="15" t="n">
-        <v>30.86</v>
-      </c>
-      <c r="H13" s="15" t="n">
-        <v>30.66</v>
-      </c>
-      <c r="I13" s="15" t="n">
-        <v>30.58</v>
-      </c>
-      <c r="J13" s="16"/>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="16"/>
-      <c r="O13" s="17"/>
-      <c r="AP13" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="AQ13" s="5" t="n">
-        <f aca="false">O24</f>
-        <v>0</v>
-      </c>
-      <c r="AR13" s="5" t="n">
-        <f aca="false">O6</f>
-        <v>0</v>
-      </c>
-      <c r="AS13" s="5" t="n">
-        <f aca="false">O7</f>
-        <v>0</v>
-      </c>
-      <c r="AT13" s="5" t="n">
-        <f aca="false">O8</f>
-        <v>0</v>
-      </c>
-      <c r="AU13" s="5" t="n">
-        <f aca="false">O9</f>
-        <v>0</v>
-      </c>
-      <c r="AV13" s="5" t="n">
-        <f aca="false">O10</f>
-        <v>0</v>
-      </c>
-      <c r="AW13" s="5" t="n">
-        <f aca="false">O11</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" s="14" t="n">
-        <f aca="false">IFERROR(AVERAGE(D14,E14,F14,G14,H14,I14),"")</f>
-        <v>17.795</v>
-      </c>
-      <c r="D14" s="15" t="n">
-        <v>15.36</v>
-      </c>
-      <c r="E14" s="15" t="n">
-        <v>14.68</v>
-      </c>
-      <c r="F14" s="15" t="n">
-        <v>17.01</v>
-      </c>
-      <c r="G14" s="15" t="n">
-        <v>19.84</v>
-      </c>
-      <c r="H14" s="15" t="n">
-        <v>20.64</v>
-      </c>
-      <c r="I14" s="15" t="n">
-        <v>19.24</v>
-      </c>
-      <c r="J14" s="16"/>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="16"/>
-      <c r="O14" s="17"/>
-    </row>
-    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="C15" s="14" t="n">
-        <f aca="false">IFERROR(AVERAGE(D15,E15,F15,G15,H15,I15),"")</f>
-        <v>15.66</v>
-      </c>
-      <c r="D15" s="15" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="E15" s="15" t="n">
-        <v>15.16</v>
-      </c>
-      <c r="F15" s="15" t="n">
-        <v>9.91</v>
-      </c>
-      <c r="G15" s="15" t="n">
-        <v>21.15</v>
-      </c>
-      <c r="H15" s="15" t="n">
-        <v>20.56</v>
-      </c>
-      <c r="I15" s="15" t="n">
-        <v>18.28</v>
-      </c>
-      <c r="J15" s="16"/>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="16"/>
-      <c r="O15" s="17"/>
-    </row>
-    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="C16" s="14" t="n">
-        <f aca="false">IFERROR(AVERAGE(D16,E16,F16,G16,H16,I16),"")</f>
-        <v>7.6</v>
-      </c>
-      <c r="D16" s="15" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="E16" s="15" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="F16" s="15" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="G16" s="15" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="H16" s="15" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="I16" s="15" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="J16" s="16"/>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="16"/>
-      <c r="O16" s="17"/>
-    </row>
-    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="C17" s="14" t="n">
-        <f aca="false">IFERROR(AVERAGE(D17,E17,F17,G17,H17,I17),"")</f>
-        <v>4.62666666666667</v>
-      </c>
-      <c r="D17" s="15" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="E17" s="15" t="n">
-        <v>4.61</v>
-      </c>
-      <c r="F17" s="15" t="n">
-        <v>6.99</v>
-      </c>
-      <c r="G17" s="15" t="n">
-        <v>4.54</v>
-      </c>
-      <c r="H17" s="15" t="n">
-        <v>4.52</v>
-      </c>
-      <c r="I17" s="15" t="n">
-        <v>4.93</v>
-      </c>
-      <c r="J17" s="16"/>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="16"/>
-      <c r="O17" s="17"/>
-    </row>
-    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="C18" s="14" t="n">
-        <f aca="false">IFERROR(AVERAGE(D18,E18,F18,G18,H18,I18),"")</f>
-        <v>4</v>
-      </c>
-      <c r="D18" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="E18" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="F18" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="G18" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="H18" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="I18" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="J18" s="16"/>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="16"/>
-      <c r="O18" s="17"/>
-    </row>
-    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C19" s="14" t="n">
-        <f aca="false">IFERROR(AVERAGE(D19,E19,F19,G19,H19,I19),"")</f>
-        <v>2.94</v>
-      </c>
-      <c r="D19" s="15" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="E19" s="15" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="F19" s="15" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="G19" s="15" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="H19" s="15" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="I19" s="15" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="J19" s="16"/>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="16"/>
-      <c r="O19" s="17"/>
-    </row>
-    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="C20" s="14" t="n">
-        <f aca="false">IFERROR(AVERAGE(D20,E20,F20,G20,H20,I20),"")</f>
-        <v>2.535</v>
-      </c>
-      <c r="D20" s="15" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="E20" s="15" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="F20" s="15" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="G20" s="15" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="H20" s="15" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="I20" s="15" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="J20" s="16"/>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="16"/>
-      <c r="O20" s="17"/>
-    </row>
-    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="C21" s="14" t="n">
-        <f aca="false">IFERROR(AVERAGE(D21,E21,F21,G21,H21,I21),"")</f>
-        <v>2.10666666666667</v>
-      </c>
-      <c r="D21" s="15" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="E21" s="15" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="F21" s="15" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="G21" s="15" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="H21" s="15" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="I21" s="15" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="J21" s="16"/>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="16"/>
-      <c r="O21" s="17"/>
-    </row>
-    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="C22" s="14" t="n">
-        <f aca="false">IFERROR(AVERAGE(D22,E22,F22,G22,H22,I22),"")</f>
-        <v>1.49166666666667</v>
-      </c>
-      <c r="D22" s="15" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="E22" s="15" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="F22" s="15" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="G22" s="15" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="H22" s="15" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="I22" s="15" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="J22" s="16"/>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="16"/>
-      <c r="O22" s="17"/>
-    </row>
-    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="C23" s="14" t="n">
-        <f aca="false">IFERROR(AVERAGE(D23,E23,F23,G23,H23,I23),"")</f>
-        <v>6.85</v>
-      </c>
-      <c r="D23" s="15" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="E23" s="15" t="n">
-        <v>6.37</v>
-      </c>
-      <c r="F23" s="15" t="n">
-        <v>6.43</v>
-      </c>
-      <c r="G23" s="15" t="n">
-        <v>7.43</v>
-      </c>
-      <c r="H23" s="15" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="I23" s="15" t="n">
-        <v>6.62</v>
-      </c>
-      <c r="J23" s="16"/>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="16"/>
-      <c r="O23" s="17"/>
-    </row>
-    <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="C24" s="21" t="n">
-        <f aca="false">IFERROR(SUM(C6,C7,C8,C9,C10,C11,C12,C13,C14,C15,C16,C17,C18,C19,C20,C21,C22,C23),"")</f>
-        <v>3608.45666666667</v>
-      </c>
-      <c r="D24" s="21" t="n">
-        <f aca="false">IFERROR(SUM(D6:D23),"")</f>
-        <v>3316.36</v>
-      </c>
-      <c r="E24" s="21" t="n">
-        <f aca="false">IFERROR(SUM(E6:E23),"")</f>
-        <v>3455.32</v>
-      </c>
-      <c r="F24" s="21" t="n">
-        <f aca="false">IFERROR(SUM(F6:F23),"")</f>
-        <v>3483.88</v>
-      </c>
-      <c r="G24" s="21" t="n">
-        <f aca="false">IFERROR(SUM(G6:G23),"")</f>
-        <v>3904.08</v>
-      </c>
-      <c r="H24" s="21" t="n">
-        <f aca="false">IFERROR(SUM(H6:H23),"")</f>
-        <v>3910.71</v>
-      </c>
-      <c r="I24" s="21" t="n">
-        <f aca="false">IFERROR(SUM(I6:I23),"")</f>
-        <v>3580.39</v>
-      </c>
-      <c r="J24" s="21" t="n">
-        <f aca="false">IFERROR(SUM(J6:J23),"")</f>
-        <v>0</v>
-      </c>
-      <c r="K24" s="21" t="n">
-        <f aca="false">IFERROR(SUM(K6:K23),"")</f>
-        <v>0</v>
-      </c>
-      <c r="L24" s="21" t="n">
-        <f aca="false">IFERROR(SUM(L6:L23),"")</f>
-        <v>0</v>
-      </c>
-      <c r="M24" s="21" t="n">
-        <f aca="false">IFERROR(SUM(M6:M23),"")</f>
-        <v>0</v>
-      </c>
-      <c r="N24" s="21" t="n">
-        <f aca="false">IFERROR(SUM(N6:N23),"")</f>
-        <v>0</v>
-      </c>
-      <c r="O24" s="21" t="n">
-        <f aca="false">IFERROR(SUM(O6:O23),"")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="C25" s="23"/>
-      <c r="D25" s="24" t="s">
-        <v>44</v>
-      </c>
-      <c r="E25" s="25" t="n">
-        <f aca="false">IFERROR(E24-D24,"")</f>
-        <v>138.96</v>
-      </c>
-      <c r="F25" s="25" t="n">
-        <f aca="false">IFERROR(F24-E24,"")</f>
-        <v>28.5599999999999</v>
-      </c>
-      <c r="G25" s="25" t="n">
-        <f aca="false">IFERROR(G24-F24,"")</f>
-        <v>420.2</v>
-      </c>
-      <c r="H25" s="25" t="n">
-        <f aca="false">IFERROR(H24-G24,"")</f>
-        <v>6.63000000000011</v>
-      </c>
-      <c r="I25" s="25" t="n">
-        <f aca="false">IFERROR(I24-H24,"")</f>
-        <v>-330.32</v>
-      </c>
-      <c r="J25" s="25" t="n">
-        <f aca="false">IFERROR(J24-I24,"")</f>
-        <v>-3580.39</v>
-      </c>
-      <c r="K25" s="25" t="n">
-        <f aca="false">IFERROR(K24-J24,"")</f>
-        <v>0</v>
-      </c>
-      <c r="L25" s="25" t="n">
-        <f aca="false">IFERROR(L24-K24,"")</f>
-        <v>0</v>
-      </c>
-      <c r="M25" s="25" t="n">
-        <f aca="false">IFERROR(M24-L24,"")</f>
-        <v>0</v>
-      </c>
-      <c r="N25" s="25" t="n">
-        <f aca="false">IFERROR(N24-M24,"")</f>
-        <v>0</v>
-      </c>
-      <c r="O25" s="25" t="n">
-        <f aca="false">IFERROR(O24-N24,"")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="22" t="s">
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B27" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="C27" s="25"/>
+      <c r="D27" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="C26" s="23"/>
-      <c r="D26" s="24" t="s">
-        <v>44</v>
-      </c>
-      <c r="E26" s="26" t="n">
-        <f aca="false">IFERROR((E24-D24)/D24,"")</f>
-        <v>0.0419013617339493</v>
-      </c>
-      <c r="F26" s="26" t="n">
-        <f aca="false">IFERROR((F24-E24)/E24,"")</f>
-        <v>0.00826551520553811</v>
-      </c>
-      <c r="G26" s="26" t="n">
-        <f aca="false">IFERROR((G24-F24)/F24,"")</f>
+      <c r="E27" s="28" t="n">
+        <f aca="false">IFERROR((E25-D25)/D25,"")</f>
+        <v>0.0419013617339494</v>
+      </c>
+      <c r="F27" s="28" t="n">
+        <f aca="false">IFERROR((F25-E25)/E25,"")</f>
+        <v>0.00826551520553824</v>
+      </c>
+      <c r="G27" s="28" t="n">
+        <f aca="false">IFERROR((G25-F25)/F25,"")</f>
         <v>0.120612650263499</v>
       </c>
-      <c r="H26" s="26" t="n">
-        <f aca="false">IFERROR((H24-G24)/G24,"")</f>
+      <c r="H27" s="28" t="n">
+        <f aca="false">IFERROR((H25-G25)/G25,"")</f>
         <v>0.00169822339706156</v>
       </c>
-      <c r="I26" s="26" t="n">
-        <f aca="false">IFERROR((I24-H24)/H24,"")</f>
+      <c r="I27" s="28" t="n">
+        <f aca="false">IFERROR((I25-H25)/H25,"")</f>
         <v>-0.0844654806927642</v>
       </c>
-      <c r="J26" s="26" t="n">
-        <f aca="false">IFERROR((J24-I24)/I24,"")</f>
+      <c r="J27" s="28" t="n">
+        <f aca="false">IFERROR((J25-I25)/I25,"")</f>
         <v>-1</v>
       </c>
-      <c r="K26" s="26" t="str">
-        <f aca="false">IFERROR((K24-J24)/J24,"")</f>
+      <c r="K27" s="28" t="str">
+        <f aca="false">IFERROR((K25-J25)/J25,"")</f>
         <v/>
       </c>
-      <c r="L26" s="26" t="str">
-        <f aca="false">IFERROR((L24-K24)/K24,"")</f>
+      <c r="L27" s="28" t="str">
+        <f aca="false">IFERROR((L25-K25)/K25,"")</f>
         <v/>
       </c>
-      <c r="M26" s="26" t="str">
-        <f aca="false">IFERROR((M24-L24)/L24,"")</f>
+      <c r="M27" s="28" t="str">
+        <f aca="false">IFERROR((M25-L25)/L25,"")</f>
         <v/>
       </c>
-      <c r="N26" s="26" t="str">
-        <f aca="false">IFERROR((N24-M24)/M24,"")</f>
+      <c r="N27" s="28" t="str">
+        <f aca="false">IFERROR((N25-M25)/M25,"")</f>
         <v/>
       </c>
-      <c r="O26" s="26" t="str">
-        <f aca="false">IFERROR((O24-N24)/N24,"")</f>
+      <c r="O27" s="28" t="str">
+        <f aca="false">IFERROR((O25-N25)/N25,"")</f>
         <v/>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="27" t="s">
-        <v>46</v>
-      </c>
-      <c r="C27" s="28"/>
-      <c r="D27" s="29" t="n">
-        <f aca="false">IFERROR(D6/D24,"")</f>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B28" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="C28" s="30"/>
+      <c r="D28" s="31" t="n">
+        <f aca="false">IFERROR(D6/D25,"")</f>
         <v>0.66468959944035</v>
       </c>
-      <c r="E27" s="29" t="n">
-        <f aca="false">IFERROR(E6/E24,"")</f>
+      <c r="E28" s="31" t="n">
+        <f aca="false">IFERROR(E6/E25,"")</f>
         <v>0.659131426322309</v>
       </c>
-      <c r="F27" s="29" t="n">
-        <f aca="false">IFERROR(F6/F24,"")</f>
+      <c r="F28" s="31" t="n">
+        <f aca="false">IFERROR(F6/F25,"")</f>
         <v>0.632780118718211</v>
       </c>
-      <c r="G27" s="29" t="n">
-        <f aca="false">IFERROR(G6/G24,"")</f>
+      <c r="G28" s="31" t="n">
+        <f aca="false">IFERROR(G6/G25,"")</f>
         <v>0.583489580131555</v>
       </c>
-      <c r="H27" s="29" t="n">
-        <f aca="false">IFERROR(H6/H24,"")</f>
+      <c r="H28" s="31" t="n">
+        <f aca="false">IFERROR(H6/H25,"")</f>
         <v>0.583091049962795</v>
       </c>
-      <c r="I27" s="29" t="n">
-        <f aca="false">IFERROR(I6/I24,"")</f>
+      <c r="I28" s="31" t="n">
+        <f aca="false">IFERROR(I6/I25,"")</f>
         <v>0.575655166057329</v>
       </c>
-      <c r="J27" s="29" t="str">
-        <f aca="false">IFERROR(J6/J24,"")</f>
+      <c r="J28" s="31" t="str">
+        <f aca="false">IFERROR(J6/J25,"")</f>
         <v/>
       </c>
-      <c r="K27" s="29" t="str">
-        <f aca="false">IFERROR(K6/K24,"")</f>
+      <c r="K28" s="31" t="str">
+        <f aca="false">IFERROR(K6/K25,"")</f>
         <v/>
       </c>
-      <c r="L27" s="29" t="str">
-        <f aca="false">IFERROR(L6/L24,"")</f>
+      <c r="L28" s="31" t="str">
+        <f aca="false">IFERROR(L6/L25,"")</f>
         <v/>
       </c>
-      <c r="M27" s="29" t="str">
-        <f aca="false">IFERROR(M6/M24,"")</f>
+      <c r="M28" s="31" t="str">
+        <f aca="false">IFERROR(M6/M25,"")</f>
         <v/>
       </c>
-      <c r="N27" s="29" t="str">
-        <f aca="false">IFERROR(N6/N24,"")</f>
+      <c r="N28" s="31" t="str">
+        <f aca="false">IFERROR(N6/N25,"")</f>
         <v/>
       </c>
-      <c r="O27" s="29" t="str">
-        <f aca="false">IFERROR(O6/O24,"")</f>
+      <c r="O28" s="31" t="str">
+        <f aca="false">IFERROR(O6/O25,"")</f>
         <v/>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="30" t="s">
-        <v>47</v>
-      </c>
-      <c r="C28" s="31"/>
-      <c r="D28" s="32" t="str">
-        <f aca="false">IFERROR(IF(D24&gt;2500,"⚠ 超過","✓ 正常"),"")</f>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B29" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="C29" s="33"/>
+      <c r="D29" s="34" t="str">
+        <f aca="false">IFERROR(IF(D25&gt;2500,"⚠ 超過","✓ 正常"),"")</f>
         <v>⚠ 超過</v>
       </c>
-      <c r="E28" s="32" t="str">
-        <f aca="false">IFERROR(IF(E24&gt;2500,"⚠ 超過","✓ 正常"),"")</f>
+      <c r="E29" s="34" t="str">
+        <f aca="false">IFERROR(IF(E25&gt;2500,"⚠ 超過","✓ 正常"),"")</f>
         <v>⚠ 超過</v>
       </c>
-      <c r="F28" s="32" t="str">
-        <f aca="false">IFERROR(IF(F24&gt;2500,"⚠ 超過","✓ 正常"),"")</f>
+      <c r="F29" s="34" t="str">
+        <f aca="false">IFERROR(IF(F25&gt;2500,"⚠ 超過","✓ 正常"),"")</f>
         <v>⚠ 超過</v>
       </c>
-      <c r="G28" s="32" t="str">
-        <f aca="false">IFERROR(IF(G24&gt;2500,"⚠ 超過","✓ 正常"),"")</f>
+      <c r="G29" s="34" t="str">
+        <f aca="false">IFERROR(IF(G25&gt;2500,"⚠ 超過","✓ 正常"),"")</f>
         <v>⚠ 超過</v>
       </c>
-      <c r="H28" s="32" t="str">
-        <f aca="false">IFERROR(IF(H24&gt;2500,"⚠ 超過","✓ 正常"),"")</f>
+      <c r="H29" s="34" t="str">
+        <f aca="false">IFERROR(IF(H25&gt;2500,"⚠ 超過","✓ 正常"),"")</f>
         <v>⚠ 超過</v>
       </c>
-      <c r="I28" s="32" t="str">
-        <f aca="false">IFERROR(IF(I24&gt;2500,"⚠ 超過","✓ 正常"),"")</f>
+      <c r="I29" s="34" t="str">
+        <f aca="false">IFERROR(IF(I25&gt;2500,"⚠ 超過","✓ 正常"),"")</f>
         <v>⚠ 超過</v>
       </c>
-      <c r="J28" s="32" t="str">
-        <f aca="false">IFERROR(IF(J24&gt;2500,"⚠ 超過","✓ 正常"),"")</f>
+      <c r="J29" s="34" t="str">
+        <f aca="false">IFERROR(IF(J25&gt;2500,"⚠ 超過","✓ 正常"),"")</f>
         <v>✓ 正常</v>
       </c>
-      <c r="K28" s="32" t="str">
-        <f aca="false">IFERROR(IF(K24&gt;2500,"⚠ 超過","✓ 正常"),"")</f>
+      <c r="K29" s="34" t="str">
+        <f aca="false">IFERROR(IF(K25&gt;2500,"⚠ 超過","✓ 正常"),"")</f>
         <v>✓ 正常</v>
       </c>
-      <c r="L28" s="32" t="str">
-        <f aca="false">IFERROR(IF(L24&gt;2500,"⚠ 超過","✓ 正常"),"")</f>
+      <c r="L29" s="34" t="str">
+        <f aca="false">IFERROR(IF(L25&gt;2500,"⚠ 超過","✓ 正常"),"")</f>
         <v>✓ 正常</v>
       </c>
-      <c r="M28" s="32" t="str">
-        <f aca="false">IFERROR(IF(M24&gt;2500,"⚠ 超過","✓ 正常"),"")</f>
+      <c r="M29" s="34" t="str">
+        <f aca="false">IFERROR(IF(M25&gt;2500,"⚠ 超過","✓ 正常"),"")</f>
         <v>✓ 正常</v>
       </c>
-      <c r="N28" s="32" t="str">
-        <f aca="false">IFERROR(IF(N24&gt;2500,"⚠ 超過","✓ 正常"),"")</f>
+      <c r="N29" s="34" t="str">
+        <f aca="false">IFERROR(IF(N25&gt;2500,"⚠ 超過","✓ 正常"),"")</f>
         <v>✓ 正常</v>
       </c>
-      <c r="O28" s="32" t="str">
-        <f aca="false">IFERROR(IF(O24&gt;2500,"⚠ 超過","✓ 正常"),"")</f>
+      <c r="O29" s="34" t="str">
+        <f aca="false">IFERROR(IF(O25&gt;2500,"⚠ 超過","✓ 正常"),"")</f>
         <v>✓ 正常</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B2:P2"/>
@@ -4269,553 +4453,553 @@
   <dimension ref="B1:F42"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="35" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="35" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="35" width="55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="35" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="35" width="22"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="33" t="s">
-        <v>48</v>
-      </c>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
+      <c r="B2" s="36" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
     </row>
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="34" t="s">
-        <v>49</v>
-      </c>
-      <c r="C4" s="35" t="s">
+      <c r="B4" s="37" t="s">
         <v>50</v>
       </c>
-      <c r="D4" s="36" t="s">
+      <c r="C4" s="38" t="s">
         <v>51</v>
       </c>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36"/>
+      <c r="D4" s="39" t="s">
+        <v>52</v>
+      </c>
+      <c r="E4" s="39"/>
+      <c r="F4" s="39"/>
     </row>
     <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="34" t="s">
-        <v>52</v>
-      </c>
-      <c r="C5" s="37" t="s">
+      <c r="B5" s="37" t="s">
         <v>53</v>
       </c>
-      <c r="D5" s="36" t="s">
+      <c r="C5" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="E5" s="36"/>
-      <c r="F5" s="36"/>
+      <c r="D5" s="39" t="s">
+        <v>55</v>
+      </c>
+      <c r="E5" s="39"/>
+      <c r="F5" s="39"/>
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="34" t="s">
-        <v>55</v>
-      </c>
-      <c r="C6" s="37" t="s">
+      <c r="B6" s="37" t="s">
         <v>56</v>
       </c>
-      <c r="D6" s="38" t="s">
+      <c r="C6" s="40" t="s">
         <v>57</v>
       </c>
-      <c r="E6" s="38"/>
-      <c r="F6" s="38"/>
+      <c r="D6" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="E6" s="41"/>
+      <c r="F6" s="41"/>
     </row>
     <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="34" t="s">
-        <v>58</v>
-      </c>
-      <c r="C7" s="37" t="s">
+      <c r="B7" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="D7" s="38" t="s">
+      <c r="C7" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="E7" s="38"/>
-      <c r="F7" s="38"/>
+      <c r="D7" s="41" t="s">
+        <v>61</v>
+      </c>
+      <c r="E7" s="41"/>
+      <c r="F7" s="41"/>
     </row>
     <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C9" s="7" t="s">
+      <c r="B9" s="42" t="s">
         <v>62</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="C9" s="42" t="s">
         <v>63</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="D9" s="42" t="s">
         <v>64</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="E9" s="42" t="s">
         <v>65</v>
       </c>
+      <c r="F9" s="42" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="39" t="s">
-        <v>66</v>
-      </c>
-      <c r="C10" s="40" t="s">
-        <v>26</v>
-      </c>
-      <c r="D10" s="41" t="s">
+      <c r="B10" s="43" t="s">
         <v>67</v>
       </c>
-      <c r="E10" s="42" t="s">
+      <c r="C10" s="44" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="45" t="s">
         <v>68</v>
       </c>
-      <c r="F10" s="43"/>
+      <c r="E10" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="F10" s="47"/>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="39" t="s">
+      <c r="B11" s="43" t="s">
+        <v>70</v>
+      </c>
+      <c r="C11" s="44" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="45" t="s">
+        <v>68</v>
+      </c>
+      <c r="E11" s="46" t="s">
         <v>69</v>
       </c>
-      <c r="C11" s="40" t="s">
-        <v>27</v>
-      </c>
-      <c r="D11" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="E11" s="42" t="s">
+      <c r="F11" s="47"/>
+    </row>
+    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="43" t="s">
+        <v>71</v>
+      </c>
+      <c r="C12" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="45" t="s">
         <v>68</v>
       </c>
-      <c r="F11" s="43"/>
-    </row>
-    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="39" t="s">
-        <v>70</v>
-      </c>
-      <c r="C12" s="40" t="s">
-        <v>4</v>
-      </c>
-      <c r="D12" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="E12" s="42" t="s">
+      <c r="E12" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="F12" s="47"/>
+    </row>
+    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="43" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13" s="44" t="s">
+        <v>73</v>
+      </c>
+      <c r="D13" s="45" t="s">
         <v>68</v>
       </c>
-      <c r="F12" s="43"/>
-    </row>
-    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="39" t="s">
-        <v>71</v>
-      </c>
-      <c r="C13" s="40" t="s">
-        <v>72</v>
-      </c>
-      <c r="D13" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="E13" s="42" t="s">
+      <c r="E13" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="F13" s="47" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B14" s="43" t="s">
+        <v>75</v>
+      </c>
+      <c r="C14" s="44" t="s">
+        <v>76</v>
+      </c>
+      <c r="D14" s="45" t="s">
         <v>68</v>
       </c>
-      <c r="F13" s="43" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="39" t="s">
-        <v>74</v>
-      </c>
-      <c r="C14" s="40" t="s">
-        <v>75</v>
-      </c>
-      <c r="D14" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="E14" s="42" t="s">
+      <c r="E14" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="F14" s="47"/>
+    </row>
+    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="43" t="s">
+        <v>77</v>
+      </c>
+      <c r="C15" s="44" t="s">
+        <v>78</v>
+      </c>
+      <c r="D15" s="45" t="s">
         <v>68</v>
       </c>
-      <c r="F14" s="43"/>
-    </row>
-    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="39" t="s">
-        <v>76</v>
-      </c>
-      <c r="C15" s="40" t="s">
-        <v>77</v>
-      </c>
-      <c r="D15" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="E15" s="42" t="s">
+      <c r="E15" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="F15" s="47" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="C16" s="44" t="s">
+        <v>32</v>
+      </c>
+      <c r="D16" s="45" t="s">
         <v>68</v>
       </c>
-      <c r="F15" s="43" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="39" t="s">
-        <v>79</v>
-      </c>
-      <c r="C16" s="40" t="s">
-        <v>31</v>
-      </c>
-      <c r="D16" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="E16" s="42" t="s">
+      <c r="E16" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="F16" s="47"/>
+    </row>
+    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="43" t="s">
+        <v>81</v>
+      </c>
+      <c r="C17" s="44" t="s">
+        <v>33</v>
+      </c>
+      <c r="D17" s="45" t="s">
         <v>68</v>
       </c>
-      <c r="F16" s="43"/>
-    </row>
-    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="39" t="s">
-        <v>80</v>
-      </c>
-      <c r="C17" s="40" t="s">
-        <v>32</v>
-      </c>
-      <c r="D17" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="E17" s="42" t="s">
+      <c r="E17" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="F17" s="47"/>
+    </row>
+    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="43" t="s">
+        <v>82</v>
+      </c>
+      <c r="C18" s="44" t="s">
+        <v>34</v>
+      </c>
+      <c r="D18" s="45" t="s">
         <v>68</v>
       </c>
-      <c r="F17" s="43"/>
-    </row>
-    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="39" t="s">
-        <v>81</v>
-      </c>
-      <c r="C18" s="40" t="s">
-        <v>33</v>
-      </c>
-      <c r="D18" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="E18" s="42" t="s">
+      <c r="E18" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="F18" s="47"/>
+    </row>
+    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="43" t="s">
+        <v>83</v>
+      </c>
+      <c r="C19" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="D19" s="45" t="s">
         <v>68</v>
       </c>
-      <c r="F18" s="43"/>
-    </row>
-    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="39" t="s">
-        <v>82</v>
-      </c>
-      <c r="C19" s="40" t="s">
-        <v>34</v>
-      </c>
-      <c r="D19" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="E19" s="42" t="s">
+      <c r="E19" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="F19" s="47"/>
+    </row>
+    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="43" t="s">
+        <v>84</v>
+      </c>
+      <c r="C20" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D20" s="45" t="s">
         <v>68</v>
       </c>
-      <c r="F19" s="43"/>
-    </row>
-    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="39" t="s">
-        <v>83</v>
-      </c>
-      <c r="C20" s="40" t="s">
-        <v>35</v>
-      </c>
-      <c r="D20" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="E20" s="42" t="s">
+      <c r="E20" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="F20" s="47"/>
+    </row>
+    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="43" t="s">
+        <v>85</v>
+      </c>
+      <c r="C21" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="D21" s="45" t="s">
+        <v>86</v>
+      </c>
+      <c r="E21" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="F21" s="48" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="43" t="s">
+        <v>88</v>
+      </c>
+      <c r="C22" s="44" t="s">
+        <v>38</v>
+      </c>
+      <c r="D22" s="45" t="s">
         <v>68</v>
       </c>
-      <c r="F20" s="43"/>
-    </row>
-    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="39" t="s">
-        <v>84</v>
-      </c>
-      <c r="C21" s="40" t="s">
-        <v>36</v>
-      </c>
-      <c r="D21" s="41" t="s">
-        <v>85</v>
-      </c>
-      <c r="E21" s="42" t="s">
+      <c r="E22" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="F22" s="47"/>
+    </row>
+    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B23" s="43" t="s">
+        <v>89</v>
+      </c>
+      <c r="C23" s="44" t="s">
+        <v>39</v>
+      </c>
+      <c r="D23" s="45" t="s">
         <v>68</v>
       </c>
-      <c r="F21" s="44" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="39" t="s">
-        <v>87</v>
-      </c>
-      <c r="C22" s="40" t="s">
-        <v>37</v>
-      </c>
-      <c r="D22" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="E22" s="42" t="s">
+      <c r="E23" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="F23" s="47"/>
+    </row>
+    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B24" s="43" t="s">
+        <v>90</v>
+      </c>
+      <c r="C24" s="44" t="s">
+        <v>40</v>
+      </c>
+      <c r="D24" s="45" t="s">
         <v>68</v>
       </c>
-      <c r="F22" s="43"/>
-    </row>
-    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="39" t="s">
-        <v>88</v>
-      </c>
-      <c r="C23" s="40" t="s">
-        <v>38</v>
-      </c>
-      <c r="D23" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="E23" s="42" t="s">
+      <c r="E24" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="F24" s="47"/>
+    </row>
+    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B25" s="43" t="s">
+        <v>91</v>
+      </c>
+      <c r="C25" s="44" t="s">
+        <v>41</v>
+      </c>
+      <c r="D25" s="45" t="s">
         <v>68</v>
       </c>
-      <c r="F23" s="43"/>
-    </row>
-    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="39" t="s">
-        <v>89</v>
-      </c>
-      <c r="C24" s="40" t="s">
-        <v>39</v>
-      </c>
-      <c r="D24" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="E24" s="42" t="s">
+      <c r="E25" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="F25" s="47"/>
+    </row>
+    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B26" s="43" t="s">
+        <v>92</v>
+      </c>
+      <c r="C26" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="D26" s="45" t="s">
         <v>68</v>
       </c>
-      <c r="F24" s="43"/>
-    </row>
-    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="39" t="s">
-        <v>90</v>
-      </c>
-      <c r="C25" s="40" t="s">
-        <v>40</v>
-      </c>
-      <c r="D25" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="E25" s="42" t="s">
-        <v>68</v>
-      </c>
-      <c r="F25" s="43"/>
-    </row>
-    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="39" t="s">
-        <v>91</v>
-      </c>
-      <c r="C26" s="40" t="s">
-        <v>41</v>
-      </c>
-      <c r="D26" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="E26" s="42" t="s">
-        <v>68</v>
-      </c>
-      <c r="F26" s="43"/>
+      <c r="E26" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="F26" s="47"/>
     </row>
     <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="39" t="s">
-        <v>92</v>
-      </c>
-      <c r="C27" s="45" t="s">
-        <v>42</v>
-      </c>
-      <c r="D27" s="42" t="s">
-        <v>44</v>
-      </c>
-      <c r="E27" s="42" t="s">
-        <v>68</v>
-      </c>
-      <c r="F27" s="44" t="s">
+      <c r="B27" s="43" t="s">
         <v>93</v>
       </c>
+      <c r="C27" s="49" t="s">
+        <v>43</v>
+      </c>
+      <c r="D27" s="46" t="s">
+        <v>45</v>
+      </c>
+      <c r="E27" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="F27" s="48" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="46" t="s">
-        <v>94</v>
-      </c>
-      <c r="C29" s="46"/>
-      <c r="D29" s="46"/>
-      <c r="E29" s="46"/>
-      <c r="F29" s="46"/>
+      <c r="B29" s="50" t="s">
+        <v>95</v>
+      </c>
+      <c r="C29" s="50"/>
+      <c r="D29" s="50"/>
+      <c r="E29" s="50"/>
+      <c r="F29" s="50"/>
     </row>
     <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="7" t="s">
+      <c r="B30" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="C30" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="D30" s="8" t="s">
+      <c r="C30" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="E30" s="8" t="s">
+      <c r="D30" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="F30" s="7" t="s">
+      <c r="E30" s="7" t="s">
         <v>98</v>
       </c>
+      <c r="F30" s="42" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="47" t="s">
-        <v>9</v>
-      </c>
-      <c r="C31" s="47" t="s">
-        <v>99</v>
-      </c>
-      <c r="D31" s="47" t="s">
+      <c r="B31" s="51" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="51" t="s">
         <v>100</v>
       </c>
-      <c r="E31" s="47" t="s">
+      <c r="D31" s="51" t="s">
         <v>101</v>
       </c>
-      <c r="F31" s="48" t="s">
+      <c r="E31" s="51" t="s">
         <v>102</v>
       </c>
+      <c r="F31" s="52" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="47" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="47" t="s">
-        <v>99</v>
-      </c>
-      <c r="D32" s="47" t="s">
-        <v>44</v>
-      </c>
-      <c r="E32" s="47" t="s">
-        <v>101</v>
-      </c>
-      <c r="F32" s="47" t="s">
-        <v>44</v>
+      <c r="B32" s="51" t="s">
+        <v>12</v>
+      </c>
+      <c r="C32" s="51" t="s">
+        <v>100</v>
+      </c>
+      <c r="D32" s="51" t="s">
+        <v>45</v>
+      </c>
+      <c r="E32" s="51" t="s">
+        <v>102</v>
+      </c>
+      <c r="F32" s="51" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="47" t="s">
-        <v>14</v>
-      </c>
-      <c r="C33" s="47" t="s">
-        <v>99</v>
-      </c>
-      <c r="D33" s="47" t="s">
-        <v>44</v>
-      </c>
-      <c r="E33" s="47" t="s">
-        <v>101</v>
-      </c>
-      <c r="F33" s="47" t="s">
-        <v>44</v>
+      <c r="B33" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="C33" s="51" t="s">
+        <v>100</v>
+      </c>
+      <c r="D33" s="51" t="s">
+        <v>45</v>
+      </c>
+      <c r="E33" s="51" t="s">
+        <v>102</v>
+      </c>
+      <c r="F33" s="51" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="47" t="s">
-        <v>15</v>
-      </c>
-      <c r="C34" s="47" t="s">
-        <v>99</v>
-      </c>
-      <c r="D34" s="47" t="s">
-        <v>44</v>
-      </c>
-      <c r="E34" s="47" t="s">
-        <v>101</v>
-      </c>
-      <c r="F34" s="47" t="s">
-        <v>44</v>
+      <c r="B34" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="C34" s="51" t="s">
+        <v>100</v>
+      </c>
+      <c r="D34" s="51" t="s">
+        <v>45</v>
+      </c>
+      <c r="E34" s="51" t="s">
+        <v>102</v>
+      </c>
+      <c r="F34" s="51" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="47" t="s">
-        <v>16</v>
-      </c>
-      <c r="C35" s="47" t="s">
-        <v>99</v>
-      </c>
-      <c r="D35" s="47" t="s">
-        <v>44</v>
-      </c>
-      <c r="E35" s="47" t="s">
-        <v>101</v>
-      </c>
-      <c r="F35" s="47" t="s">
-        <v>44</v>
+      <c r="B35" s="51" t="s">
+        <v>17</v>
+      </c>
+      <c r="C35" s="51" t="s">
+        <v>100</v>
+      </c>
+      <c r="D35" s="51" t="s">
+        <v>45</v>
+      </c>
+      <c r="E35" s="51" t="s">
+        <v>102</v>
+      </c>
+      <c r="F35" s="51" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="47" t="s">
-        <v>17</v>
-      </c>
-      <c r="C36" s="47" t="s">
-        <v>99</v>
-      </c>
-      <c r="D36" s="47" t="s">
-        <v>44</v>
-      </c>
-      <c r="E36" s="47" t="s">
-        <v>101</v>
-      </c>
-      <c r="F36" s="47" t="s">
-        <v>44</v>
+      <c r="B36" s="51" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="51" t="s">
+        <v>100</v>
+      </c>
+      <c r="D36" s="51" t="s">
+        <v>45</v>
+      </c>
+      <c r="E36" s="51" t="s">
+        <v>102</v>
+      </c>
+      <c r="F36" s="51" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="49" t="s">
-        <v>18</v>
-      </c>
-      <c r="C37" s="49"/>
-      <c r="D37" s="49"/>
-      <c r="E37" s="49"/>
-      <c r="F37" s="49"/>
+      <c r="B37" s="53" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" s="53"/>
+      <c r="D37" s="53"/>
+      <c r="E37" s="53"/>
+      <c r="F37" s="53"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="49" t="s">
-        <v>19</v>
-      </c>
-      <c r="C38" s="49"/>
-      <c r="D38" s="49"/>
-      <c r="E38" s="49"/>
-      <c r="F38" s="49"/>
+      <c r="B38" s="53" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="53"/>
+      <c r="D38" s="53"/>
+      <c r="E38" s="53"/>
+      <c r="F38" s="53"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B39" s="49" t="s">
-        <v>20</v>
-      </c>
-      <c r="C39" s="49"/>
-      <c r="D39" s="49"/>
-      <c r="E39" s="49"/>
-      <c r="F39" s="49"/>
+      <c r="B39" s="53" t="s">
+        <v>21</v>
+      </c>
+      <c r="C39" s="53"/>
+      <c r="D39" s="53"/>
+      <c r="E39" s="53"/>
+      <c r="F39" s="53"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B40" s="49" t="s">
-        <v>21</v>
-      </c>
-      <c r="C40" s="49"/>
-      <c r="D40" s="49"/>
-      <c r="E40" s="49"/>
-      <c r="F40" s="49"/>
+      <c r="B40" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="C40" s="53"/>
+      <c r="D40" s="53"/>
+      <c r="E40" s="53"/>
+      <c r="F40" s="53"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B41" s="49" t="s">
-        <v>22</v>
-      </c>
-      <c r="C41" s="49"/>
-      <c r="D41" s="49"/>
-      <c r="E41" s="49"/>
-      <c r="F41" s="49"/>
+      <c r="B41" s="53" t="s">
+        <v>23</v>
+      </c>
+      <c r="C41" s="53"/>
+      <c r="D41" s="53"/>
+      <c r="E41" s="53"/>
+      <c r="F41" s="53"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B42" s="49" t="s">
-        <v>23</v>
-      </c>
-      <c r="C42" s="49"/>
-      <c r="D42" s="49"/>
-      <c r="E42" s="49"/>
-      <c r="F42" s="49"/>
+      <c r="B42" s="53" t="s">
+        <v>24</v>
+      </c>
+      <c r="C42" s="53"/>
+      <c r="D42" s="53"/>
+      <c r="E42" s="53"/>
+      <c r="F42" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="6">
